--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487548_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487548_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1799</v>
+        <v>11.0432</v>
       </c>
       <c r="E2" t="n">
-        <v>9.9521</v>
+        <v>10.949</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2279</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>4.9037</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.195</v>
+        <v>0.6683</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0159</v>
+        <v>1.0128</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2108</v>
+        <v>-0.3445</v>
       </c>
       <c r="V2" t="n">
         <v>3.3169</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.6205</v>
+        <v>7.716</v>
       </c>
       <c r="E3" t="n">
-        <v>9.099399999999999</v>
+        <v>7.4356</v>
       </c>
       <c r="F3" t="n">
-        <v>0.521</v>
+        <v>0.2805</v>
       </c>
       <c r="G3" t="n">
         <v>3.9681</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2606</v>
+        <v>2.3562</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7835</v>
+        <v>2.1196</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4772</v>
+        <v>0.2366</v>
       </c>
       <c r="V3" t="n">
         <v>0.6083</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4698</v>
+        <v>4.6002</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6266</v>
+        <v>5.8907</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1568</v>
+        <v>-1.2905</v>
       </c>
       <c r="G4" t="n">
         <v>2.7867</v>
@@ -766,13 +766,13 @@
         <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4873</v>
+        <v>0.6177</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6693</v>
+        <v>0.9334</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.182</v>
+        <v>-0.3157</v>
       </c>
       <c r="V4" t="n">
         <v>0.6083</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1324</v>
+        <v>0.8204</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5417</v>
+        <v>0.4389</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6741</v>
+        <v>0.3816</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4486</v>
+        <v>-0.0565</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9885</v>
+        <v>0.1708</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4601</v>
+        <v>-0.2273</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9798</v>
+        <v>-0.271</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9394</v>
+        <v>1.053</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0404</v>
+        <v>-1.3241</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5312</v>
+        <v>0.2145</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.951</v>
+        <v>-0.8822</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4197</v>
+        <v>1.0968</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5395</v>
+        <v>0.6811</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7722</v>
+        <v>0.7099</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2327</v>
+        <v>-0.0288</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4384</v>
+        <v>0.1017</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0875</v>
+        <v>1.0699</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5259</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7158</v>
+        <v>1.4486</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1764</v>
+        <v>0.9885</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4605</v>
+        <v>0.4601</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0123</v>
+        <v>1.9798</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7245</v>
+        <v>1.9394</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2877</v>
+        <v>0.0404</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7281</v>
+        <v>-0.5312</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9009</v>
+        <v>-0.951</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1728</v>
+        <v>0.4197</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6323</v>
+        <v>-0.3054</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0338</v>
+        <v>-0.2441</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4015</v>
+        <v>-0.0613</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.159</v>
+        <v>-1.8249</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X6" t="n">
         <v>-1.159</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>M. AGRASO VARELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4652</v>
+        <v>-0.7366</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2115</v>
+        <v>0.2877</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6766</v>
+        <v>-1.0243</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2516</v>
+        <v>-0.1289</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.605</v>
+        <v>-0.2654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3534</v>
+        <v>0.1364</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3014</v>
+        <v>0.3471</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6856</v>
+        <v>0.3471</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6159</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.553</v>
+        <v>-0.476</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2905</v>
+        <v>-0.6125</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2625</v>
+        <v>0.1364</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2369</v>
+        <v>-0.3323</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8893</v>
+        <v>-0.0594</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6524</v>
+        <v>-0.2729</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3329</v>
+        <v>-0.2754</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3329</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6379</v>
+        <v>-0.8594000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8056</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1677</v>
+        <v>-1.5162</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0565</v>
+        <v>-0.2516</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1708</v>
+        <v>-0.605</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2273</v>
+        <v>0.3534</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.271</v>
+        <v>1.3014</v>
       </c>
       <c r="K8" t="n">
-        <v>1.053</v>
+        <v>0.6856</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3241</v>
+        <v>0.6159</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2145</v>
+        <v>-1.553</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8822</v>
+        <v>-1.2905</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0968</v>
+        <v>-0.2625</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7773</v>
+        <v>-0.1573</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5346</v>
+        <v>0.3346</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2427</v>
+        <v>-0.492</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. AGRASO VARELA</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7366</v>
+        <v>-1.0465</v>
       </c>
       <c r="E9" t="n">
+        <v>0.5329</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.5794</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.7158</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1.1764</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4605</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.0123</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7245</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.2877</v>
       </c>
-      <c r="F9" t="n">
-        <v>-1.0243</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.1289</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.2654</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1364</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.3471</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.3471</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
-        <v>-0.476</v>
+        <v>-1.7281</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6125</v>
+        <v>-1.9009</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1364</v>
+        <v>0.1728</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3323</v>
+        <v>1.0242</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0594</v>
+        <v>1.4792</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2729</v>
+        <v>-0.4549</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2754</v>
+        <v>-1.159</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2754</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4861</v>
+        <v>-2.5837</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7143</v>
+        <v>-0.1862</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7718</v>
+        <v>-2.3976</v>
       </c>
       <c r="G10" t="n">
         <v>0.4605</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7508</v>
+        <v>-0.8484</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3694</v>
+        <v>0.1588</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3814</v>
+        <v>-1.0072</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9822</v>
+        <v>-3.7729</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6731</v>
+        <v>-2.5707</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3091</v>
+        <v>-1.2022</v>
       </c>
       <c r="G11" t="n">
         <v>-1.879</v>
@@ -1312,13 +1312,13 @@
         <v>0.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2403</v>
+        <v>-1.031</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8244</v>
+        <v>-0.7175</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2754</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.3914</v>
+        <v>15.2824</v>
       </c>
       <c r="E12" t="n">
-        <v>23.61349999999999</v>
+        <v>24.5046</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.222</v>
+        <v>-9.222099999999999</v>
       </c>
       <c r="G12" t="n">
         <v>10.5358</v>
       </c>
       <c r="H12" t="n">
-        <v>1.692600000000001</v>
+        <v>1.6926</v>
       </c>
       <c r="I12" t="n">
         <v>8.843</v>
@@ -1369,7 +1369,7 @@
         <v>14.9311</v>
       </c>
       <c r="L12" t="n">
-        <v>6.562799999999998</v>
+        <v>6.562799999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-10.9583</v>
@@ -1390,16 +1390,16 @@
         <v>10.7715</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7819</v>
+        <v>2.673100000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>5.2404</v>
+        <v>6.1313</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.4582</v>
+        <v>-3.458200000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1150999999999996</v>
+        <v>0.1151000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>5.6925</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3348</v>
+        <v>1.7144</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7167</v>
+        <v>5.3074</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3819</v>
+        <v>-3.593</v>
       </c>
       <c r="G13" t="n">
         <v>0.0542</v>
@@ -1468,13 +1468,13 @@
         <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5133</v>
+        <v>0.8929</v>
       </c>
       <c r="T13" t="n">
-        <v>1.398</v>
+        <v>0.9886</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1153</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.159</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.294</v>
+        <v>0.6051</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1897</v>
+        <v>0.6274</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.8958</v>
+        <v>-0.0223</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.1473</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0902</v>
+        <v>0.3073</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0056</v>
+        <v>-0.4546</v>
       </c>
       <c r="J14" t="n">
-        <v>3.848</v>
+        <v>-0.2306</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1265</v>
+        <v>1.053</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7215</v>
+        <v>-1.2836</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.7634</v>
+        <v>0.0833</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0363</v>
+        <v>-0.7458</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7271</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R14" t="n">
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9927</v>
+        <v>-0.0518</v>
       </c>
       <c r="T14" t="n">
-        <v>2.496</v>
+        <v>0.2082</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5033</v>
+        <v>-0.26</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.8249</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6097</v>
+        <v>0.5766</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5251</v>
+        <v>2.9617</v>
       </c>
       <c r="F15" t="n">
+        <v>-2.3851</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.08459999999999999</v>
       </c>
-      <c r="G15" t="n">
-        <v>-0.1473</v>
-      </c>
       <c r="H15" t="n">
-        <v>0.3073</v>
+        <v>0.0902</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4546</v>
+        <v>-0.0056</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2306</v>
+        <v>3.848</v>
       </c>
       <c r="K15" t="n">
-        <v>1.053</v>
+        <v>2.1265</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2836</v>
+        <v>1.7215</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0833</v>
+        <v>-3.7634</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7458</v>
+        <v>-2.0363</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8290999999999999</v>
+        <v>-1.7271</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1958</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R15" t="n">
         <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0472</v>
+        <v>1.2754</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1059</v>
+        <v>1.268</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.153</v>
+        <v>0.0074</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1919</v>
+        <v>-0.4977</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4062</v>
+        <v>-0.7922</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2143</v>
+        <v>0.2945</v>
       </c>
       <c r="G16" t="n">
         <v>0.8116</v>
@@ -1702,13 +1702,13 @@
         <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4539</v>
+        <v>-0.7597</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8316</v>
+        <v>-0.2176</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6223</v>
+        <v>-0.5421</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9412</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8562</v>
+        <v>-1.9585</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7815</v>
+        <v>-0.8838</v>
       </c>
       <c r="F17" t="n">
         <v>-1.0747</v>
@@ -1780,10 +1780,10 @@
         <v>0.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1575</v>
+        <v>-1.2598</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.09</v>
+        <v>-0.1923</v>
       </c>
       <c r="U17" t="n">
         <v>-1.0675</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9187</v>
+        <v>-2.788</v>
       </c>
       <c r="E18" t="n">
-        <v>2.926</v>
+        <v>2.1073</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.8446</v>
+        <v>-4.8953</v>
       </c>
       <c r="G18" t="n">
         <v>-2.7104</v>
@@ -1858,13 +1858,13 @@
         <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.771</v>
+        <v>-0.0984</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5585</v>
+        <v>0.7399</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7876</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0.6083</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1461</v>
+        <v>-3.3021</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2404</v>
+        <v>-0.1545</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.3865</v>
+        <v>-3.1476</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.9443</v>
+        <v>-2.3502</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5291</v>
+        <v>-2.886</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4153</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8445</v>
+        <v>1.5475</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1719</v>
+        <v>-0.4425</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6726</v>
+        <v>1.99</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0999</v>
+        <v>-3.8978</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3572</v>
+        <v>-2.4436</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7427</v>
+        <v>-1.4542</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5935</v>
+        <v>0.1645</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1317</v>
+        <v>0.5099</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4617</v>
+        <v>-0.3454</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2166</v>
+        <v>-0.0576</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4932</v>
+        <v>-4.0262</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0755</v>
+        <v>0.5474</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4177</v>
+        <v>-4.5736</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3502</v>
+        <v>-3.9443</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.886</v>
+        <v>-1.5291</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5358000000000001</v>
+        <v>-2.4153</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5475</v>
+        <v>-0.8445</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4425</v>
+        <v>-0.1719</v>
       </c>
       <c r="L20" t="n">
-        <v>1.99</v>
+        <v>-0.6726</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.8978</v>
+        <v>-3.0999</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4436</v>
+        <v>-1.3572</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4542</v>
+        <v>-1.7427</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0266</v>
+        <v>-0.4736</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4111</v>
+        <v>0.1753</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6155</v>
+        <v>-0.6489</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0576</v>
+        <v>1.2166</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0238</v>
+        <v>-4.0328</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1126</v>
+        <v>-0.4986</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9112</v>
+        <v>-3.5342</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2226</v>
@@ -2092,13 +2092,13 @@
         <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7805</v>
+        <v>-0.7894</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6358</v>
+        <v>-0.0218</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1447</v>
+        <v>-0.7677</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2166</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-14.3914</v>
+        <v>-13.7092</v>
       </c>
       <c r="E22" t="n">
         <v>9.222100000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-23.6135</v>
+        <v>-22.9313</v>
       </c>
       <c r="G22" t="n">
         <v>-10.5356</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.692499999999999</v>
+        <v>-1.6925</v>
       </c>
       <c r="I22" t="n">
         <v>-8.843200000000001</v>
@@ -2170,22 +2170,22 @@
         <v>8.812999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7822</v>
+        <v>-1.0999</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4582</v>
+        <v>3.458200000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.2403</v>
+        <v>-4.5581</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1151</v>
+        <v>-0.1150999999999998</v>
       </c>
       <c r="W22" t="n">
         <v>5.577299999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-5.6925</v>
+        <v>-5.692499999999999</v>
       </c>
     </row>
   </sheetData>
